--- a/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2018_T2_0.xlsx
+++ b/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2018_T2_0.xlsx
@@ -45,7 +45,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>91</t>
+    <t>87</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -57,40 +57,40 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>0.286</t>
-  </si>
-  <si>
-    <t>(0.048)</t>
-  </si>
-  <si>
-    <t>0.484</t>
-  </si>
-  <si>
-    <t>(0.053)</t>
-  </si>
-  <si>
-    <t>0.231</t>
-  </si>
-  <si>
-    <t>(0.044)</t>
-  </si>
-  <si>
-    <t>0.835</t>
-  </si>
-  <si>
-    <t>(0.238)</t>
-  </si>
-  <si>
-    <t>1.231</t>
-  </si>
-  <si>
-    <t>(0.198)</t>
-  </si>
-  <si>
-    <t>0.352</t>
-  </si>
-  <si>
-    <t>(0.083)</t>
+    <t>0.299</t>
+  </si>
+  <si>
+    <t>(0.049)</t>
+  </si>
+  <si>
+    <t>0.506</t>
+  </si>
+  <si>
+    <t>(0.054)</t>
+  </si>
+  <si>
+    <t>0.241</t>
+  </si>
+  <si>
+    <t>(0.046)</t>
+  </si>
+  <si>
+    <t>0.874</t>
+  </si>
+  <si>
+    <t>(0.248)</t>
+  </si>
+  <si>
+    <t>1.287</t>
+  </si>
+  <si>
+    <t>(0.205)</t>
+  </si>
+  <si>
+    <t>0.368</t>
+  </si>
+  <si>
+    <t>(0.087)</t>
   </si>
   <si>
     <t>23</t>
@@ -138,7 +138,7 @@
     <t>(0.229)</t>
   </si>
   <si>
-    <t>114</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -150,22 +150,22 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>0.236**</t>
-  </si>
-  <si>
-    <t>0.343***</t>
-  </si>
-  <si>
-    <t>0.508***</t>
-  </si>
-  <si>
-    <t>1.252</t>
-  </si>
-  <si>
-    <t>2.117***</t>
-  </si>
-  <si>
-    <t>0.909***</t>
+    <t>0.223**</t>
+  </si>
+  <si>
+    <t>0.320***</t>
+  </si>
+  <si>
+    <t>0.498***</t>
+  </si>
+  <si>
+    <t>1.213</t>
+  </si>
+  <si>
+    <t>2.060***</t>
+  </si>
+  <si>
+    <t>0.893***</t>
   </si>
 </sst>
 </file>
